--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488204_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488204_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8449</v>
+        <v>7.0462</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2658</v>
+        <v>3.5163</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5791</v>
+        <v>3.5299</v>
       </c>
       <c r="G2" t="n">
         <v>5.1394</v>
@@ -610,13 +610,13 @@
         <v>3.3352</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1087</v>
+        <v>0.0926</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6939</v>
+        <v>-0.4433</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.5359</v>
       </c>
       <c r="V2" t="n">
         <v>1.2583</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6626</v>
+        <v>6.1768</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5735</v>
+        <v>3.0632</v>
       </c>
       <c r="F3" t="n">
-        <v>3.089</v>
+        <v>3.1137</v>
       </c>
       <c r="G3" t="n">
         <v>4.9276</v>
@@ -688,13 +688,13 @@
         <v>2.2234</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8764</v>
+        <v>-0.3622</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0943</v>
+        <v>-0.6047</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2178</v>
+        <v>0.2425</v>
       </c>
       <c r="V3" t="n">
         <v>0.3144</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.399</v>
+        <v>5.6939</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3128</v>
+        <v>3.4107</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0862</v>
+        <v>2.2832</v>
       </c>
       <c r="G4" t="n">
         <v>1.2778</v>
@@ -766,13 +766,13 @@
         <v>2.4087</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1758</v>
+        <v>0.1191</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3109</v>
+        <v>-0.2129</v>
       </c>
       <c r="U4" t="n">
-        <v>0.135</v>
+        <v>0.332</v>
       </c>
       <c r="V4" t="n">
         <v>1.8883</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.1159</v>
+        <v>3.8959</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3772</v>
+        <v>1.4527</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7387</v>
+        <v>2.4432</v>
       </c>
       <c r="G5" t="n">
         <v>1.5501</v>
@@ -844,13 +844,13 @@
         <v>2.594</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6012</v>
+        <v>0.3811</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7000999999999999</v>
+        <v>-0.2244</v>
       </c>
       <c r="U5" t="n">
-        <v>0.901</v>
+        <v>0.6056</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6294</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5054</v>
+        <v>3.2225</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7691</v>
+        <v>3.5848</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2638</v>
+        <v>-0.3623</v>
       </c>
       <c r="G6" t="n">
         <v>2.1296</v>
@@ -922,13 +922,13 @@
         <v>1.1117</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5785</v>
+        <v>0.2956</v>
       </c>
       <c r="T6" t="n">
-        <v>0.291</v>
+        <v>0.1066</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2875</v>
+        <v>0.189</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3144</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. HEPBURN</t>
+          <t>A. GALLEGO GÓMEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5698</v>
+        <v>1.5662</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9975</v>
+        <v>1.5662</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4277</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5496</v>
+        <v>1.5662</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5603</v>
+        <v>0.3221</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0107</v>
+        <v>1.2441</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9612</v>
+        <v>1.5662</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4482</v>
+        <v>0.3221</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.487</v>
+        <v>1.2441</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4115</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8878</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4763</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1477</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0373</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1104</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. GALLEGO GÓMEZ</t>
+          <t>P. HEPBURN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5662</v>
+        <v>1.41</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5662</v>
+        <v>1.8131</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-0.4031</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5662</v>
+        <v>2.5496</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3221</v>
+        <v>2.5603</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2441</v>
+        <v>-0.0107</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5662</v>
+        <v>2.9612</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3221</v>
+        <v>3.4482</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2441</v>
+        <v>-0.487</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-0.4115</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.8878</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.4763</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.3075</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.2216</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.0858</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1273</v>
+        <v>1.1519</v>
       </c>
       <c r="E9" t="n">
         <v>1.2391</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1119</v>
+        <v>-0.0872</v>
       </c>
       <c r="G9" t="n">
         <v>0.8497</v>
@@ -1156,13 +1156,13 @@
         <v>0.3706</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.093</v>
+        <v>-0.0684</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1094</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.8103</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6381</v>
+        <v>-1.4307</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3149</v>
+        <v>2.2411</v>
       </c>
       <c r="G10" t="n">
         <v>2.2718</v>
@@ -1234,13 +1234,13 @@
         <v>1.6676</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4832</v>
+        <v>-0.3498</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.766</v>
+        <v>-0.5586</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2828</v>
+        <v>0.2089</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0792</v>
+        <v>-0.9566</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5673</v>
+        <v>-0.4694</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5119</v>
+        <v>-0.4872</v>
       </c>
       <c r="G11" t="n">
         <v>-1.302</v>
@@ -1312,13 +1312,13 @@
         <v>0.1853</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0376</v>
+        <v>0.1601</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0211</v>
+        <v>0.1191</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0087</v>
+        <v>-1.9348</v>
       </c>
       <c r="E12" t="n">
         <v>-1.6855</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3232</v>
+        <v>-0.2493</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8915</v>
@@ -1390,13 +1390,13 @@
         <v>0.3706</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5613</v>
+        <v>-0.4875</v>
       </c>
       <c r="T12" t="n">
         <v>-0.2736</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2878</v>
+        <v>-0.2139</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V. PIETUKHOV</t>
+          <t>A. GALLEGO GOMEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.5861</v>
+        <v>-3.1651</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.5232</v>
+        <v>-2.8586</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0629</v>
+        <v>-0.3065</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3646</v>
+        <v>-1.7474</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.0573</v>
+        <v>-0.5385</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6927</v>
+        <v>-1.2088</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.0496</v>
+        <v>-1.3505</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1125</v>
+        <v>-0.2107</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06279999999999999</v>
+        <v>-1.1398</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6850000000000001</v>
+        <v>-0.3968</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0552</v>
+        <v>-0.3278</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6299</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9264</v>
+        <v>1.6676</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.9</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5471</v>
+        <v>-0.5816</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4728</v>
+        <v>-0.3184</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.1471</v>
+        <v>-1.2589</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.1471</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. GALLEGO GOMEZ</t>
+          <t>V. PIETUKHOV</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.8145</v>
+        <v>-3.3908</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.2618</v>
+        <v>-2.2294</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5527</v>
+        <v>-1.1614</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.7474</v>
+        <v>-0.3646</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5385</v>
+        <v>-1.0573</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.2088</v>
+        <v>0.6927</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.3505</v>
+        <v>-1.0496</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2107</v>
+        <v>-1.1125</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.1398</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3968</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3278</v>
+        <v>0.0552</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.6299</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6676</v>
+        <v>0.9264</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5494</v>
+        <v>0.1209</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9849</v>
+        <v>-0.2534</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5646</v>
+        <v>0.3743</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2589</v>
+        <v>-3.1471</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2589</v>
+        <v>-3.1471</v>
       </c>
     </row>
     <row r="15">
@@ -1579,19 +1579,19 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>20.9795</v>
+        <v>21.5264</v>
       </c>
       <c r="E15" t="n">
-        <v>10.4253</v>
+        <v>10.9725</v>
       </c>
       <c r="F15" t="n">
-        <v>10.5538</v>
+        <v>10.5541</v>
       </c>
       <c r="G15" t="n">
         <v>17.9563</v>
       </c>
       <c r="H15" t="n">
-        <v>7.703600000000001</v>
+        <v>7.7036</v>
       </c>
       <c r="I15" t="n">
         <v>10.2527</v>
@@ -1624,10 +1624,10 @@
         <v>18.5287</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.8526</v>
+        <v>-1.306</v>
       </c>
       <c r="T15" t="n">
-        <v>-3.8052</v>
+        <v>-3.2578</v>
       </c>
       <c r="U15" t="n">
         <v>1.9521</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. TRAORE</t>
+          <t>F. GERONIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.216</v>
+        <v>1.2712</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6629</v>
+        <v>-0.6727</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4469</v>
+        <v>1.9439</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4782</v>
+        <v>0.0165</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4724</v>
+        <v>-0.0435</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9506</v>
+        <v>0.0599</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2883</v>
+        <v>-0.4626</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1639</v>
+        <v>0.1074</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1244</v>
+        <v>-0.5699</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.7665</v>
+        <v>0.479</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6915</v>
+        <v>-0.1508</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.075</v>
+        <v>0.6299</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.297</v>
+        <v>0.9264</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4823</v>
+        <v>0.9264</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3618</v>
+        <v>0.3283</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9511</v>
+        <v>-0.2101</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4106</v>
+        <v>0.5384</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2027</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. GERONIN</t>
+          <t>H. GREVELS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.1699</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0644</v>
+        <v>-1.0704</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9439</v>
+        <v>1.2402</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0165</v>
+        <v>-0.6419</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0435</v>
+        <v>1.0556</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0599</v>
+        <v>-1.6974</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4626</v>
+        <v>-0.9494</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1074</v>
+        <v>1.0092</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5699</v>
+        <v>-1.9586</v>
       </c>
       <c r="M18" t="n">
-        <v>0.479</v>
+        <v>0.3076</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1508</v>
+        <v>0.0464</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6299</v>
+        <v>0.2611</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9264</v>
+        <v>0.7411</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9264</v>
+        <v>0.7411</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0634</v>
+        <v>0.0706</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6019</v>
+        <v>-0.1209</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5384</v>
+        <v>0.1915</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. GREVELS</t>
+          <t>F. QUINTERO DE ARMAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0227</v>
+        <v>0.0396</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1683</v>
+        <v>0.1405</v>
       </c>
       <c r="F19" t="n">
-        <v>1.191</v>
+        <v>-0.1009</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6419</v>
+        <v>-0.3468</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0556</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6974</v>
+        <v>-0.2841</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9494</v>
+        <v>0.0215</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0092</v>
+        <v>0.0215</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.9586</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3076</v>
+        <v>-0.3683</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0464</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2611</v>
+        <v>-0.2841</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7411</v>
+        <v>0.1853</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7411</v>
+        <v>0.1853</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0766</v>
+        <v>0.2011</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2189</v>
+        <v>0.1191</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1423</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. QUINTERO DE ARMAS</t>
+          <t>I. TRAORE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1076</v>
+        <v>0.0175</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0426</v>
+        <v>1.9002</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1502</v>
+        <v>-1.8826</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3468</v>
+        <v>-0.4782</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.06270000000000001</v>
+        <v>0.4724</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2841</v>
+        <v>-0.9506</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0215</v>
+        <v>2.2883</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0215</v>
+        <v>2.1639</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.1244</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3683</v>
+        <v>-2.7665</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-1.6915</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2841</v>
+        <v>-1.075</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1853</v>
+        <v>-1.297</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1853</v>
+        <v>1.4823</v>
       </c>
       <c r="S20" t="n">
-        <v>0.054</v>
+        <v>1.1633</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0211</v>
+        <v>0.1884</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0328</v>
+        <v>0.9749</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.2027</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7419</v>
+        <v>-0.6927</v>
       </c>
       <c r="E21" t="n">
         <v>0.008200000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7502</v>
+        <v>-0.7009</v>
       </c>
       <c r="G21" t="n">
         <v>-0.7201</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0219</v>
+        <v>0.0274</v>
       </c>
       <c r="T21" t="n">
         <v>-0.0547</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0328</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. MARKWARDT FERNANDES</t>
+          <t>I. FERNANDEZ MEGIAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9957</v>
+        <v>-0.8017</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9929</v>
+        <v>-1.3322</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0028</v>
+        <v>0.5304</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4242</v>
+        <v>-1.4099</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4242</v>
+        <v>-0.6511</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-0.7588</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0429</v>
+        <v>-0.723</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0429</v>
+        <v>-0.1637</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-0.5592</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4671</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4671</v>
+        <v>-0.4874</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>-0.1996</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3706</v>
+        <v>0.9264</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0157</v>
+        <v>0.2758</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1094</v>
+        <v>-0.0152</v>
       </c>
       <c r="U22" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.291</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.0845</v>
+        <v>-0.9304</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9131</v>
+        <v>1.109</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9976</v>
+        <v>-2.0394</v>
       </c>
       <c r="G23" t="n">
         <v>-1.1113</v>
@@ -2248,13 +2248,13 @@
         <v>1.1117</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8028</v>
+        <v>0.9569</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0373</v>
+        <v>0.1586</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8401</v>
+        <v>0.7983</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8877</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I. FERNANDEZ MEGIAS</t>
+          <t>R. MARKWARDT FERNANDES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2026</v>
+        <v>-1.0696</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4301</v>
+        <v>-0.9929</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2275</v>
+        <v>-0.0767</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.4099</v>
+        <v>-0.4242</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6511</v>
+        <v>-0.4242</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7588</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.723</v>
+        <v>0.0429</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1637</v>
+        <v>0.0429</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5592</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.4671</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4874</v>
+        <v>-0.4671</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1996</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
+        <v>-0.5558999999999999</v>
+      </c>
+      <c r="Q24" t="n">
         <v>-0.9264</v>
       </c>
-      <c r="Q24" t="n">
-        <v>-1.8529</v>
-      </c>
       <c r="R24" t="n">
-        <v>0.9264</v>
+        <v>0.3706</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1251</v>
+        <v>-0.0895</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1131</v>
+        <v>-0.1094</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.012</v>
+        <v>0.0199</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8915</v>
+        <v>-3.6705</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5027</v>
+        <v>-2.4048</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3888</v>
+        <v>-1.2656</v>
       </c>
       <c r="G25" t="n">
         <v>-2.9041</v>
@@ -2404,13 +2404,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6168</v>
+        <v>-0.3958</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7113</v>
+        <v>-0.6133999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0945</v>
+        <v>0.2176</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.1779</v>
+        <v>-4.41</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.926</v>
+        <v>-1.4364</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.2519</v>
+        <v>-2.9736</v>
       </c>
       <c r="G26" t="n">
         <v>-4.4277</v>
@@ -2482,13 +2482,13 @@
         <v>1.1117</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.9709</v>
+        <v>-0.203</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9637</v>
+        <v>-0.4741</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0072</v>
+        <v>0.2711</v>
       </c>
       <c r="V26" t="n">
         <v>1.8883</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.3482</v>
+        <v>-4.4566</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.9162</v>
+        <v>-1.5245</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.432</v>
+        <v>-2.9321</v>
       </c>
       <c r="G27" t="n">
         <v>-1.2881</v>
@@ -2560,13 +2560,13 @@
         <v>1.297</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.7598</v>
+        <v>0.1318</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.6392</v>
+        <v>-0.2474</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.1206</v>
+        <v>0.3793</v>
       </c>
       <c r="V27" t="n">
         <v>1.8877</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-6.5137</v>
+        <v>-6.7594</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.1463</v>
+        <v>-5.2442</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.3674</v>
+        <v>-1.5151</v>
       </c>
       <c r="G28" t="n">
         <v>-5.1868</v>
@@ -2638,13 +2638,13 @@
         <v>1.4823</v>
       </c>
       <c r="S28" t="n">
-        <v>0.2845</v>
+        <v>0.0389</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.475</v>
+        <v>-0.5729</v>
       </c>
       <c r="U28" t="n">
-        <v>0.7595</v>
+        <v>0.6118</v>
       </c>
       <c r="V28" t="n">
         <v>-0.3144</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-20.9792</v>
+        <v>-20.3265</v>
       </c>
       <c r="E29" t="n">
-        <v>-10.5539</v>
+        <v>-10.554</v>
       </c>
       <c r="F29" t="n">
-        <v>-10.4254</v>
+        <v>-9.772400000000001</v>
       </c>
       <c r="G29" t="n">
         <v>-17.9564</v>
@@ -2689,10 +2689,10 @@
         <v>-10.2528</v>
       </c>
       <c r="J29" t="n">
-        <v>1.4303</v>
+        <v>1.430299999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>5.425499999999998</v>
+        <v>5.4255</v>
       </c>
       <c r="L29" t="n">
         <v>-3.994999999999999</v>
@@ -2716,13 +2716,13 @@
         <v>10.1907</v>
       </c>
       <c r="S29" t="n">
-        <v>1.852900000000001</v>
+        <v>2.5058</v>
       </c>
       <c r="T29" t="n">
-        <v>-1.9523</v>
+        <v>-1.952</v>
       </c>
       <c r="U29" t="n">
-        <v>3.805</v>
+        <v>4.458</v>
       </c>
       <c r="V29" t="n">
         <v>3.4622</v>
